--- a/src/nodes/HPC/compressor_stage_2_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_2_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-18.379220738620816</v>
+        <v>-18.422351711139434</v>
       </c>
       <c r="B1">
-        <v>12.508214096788983</v>
+        <v>12.44460253608519</v>
       </c>
       <c r="C1">
         <v>190.54511692961938</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-16.543552351295116</v>
+        <v>-16.634369550125307</v>
       </c>
       <c r="B2">
-        <v>12.77771711692734</v>
+        <v>12.665115892280584</v>
       </c>
       <c r="C2">
         <v>190.54511692961938</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-15.156355594052299</v>
+        <v>-15.263977049829771</v>
       </c>
       <c r="B3">
-        <v>12.520037890452791</v>
+        <v>12.39129656545215</v>
       </c>
       <c r="C3">
         <v>190.54511692961938</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-13.840785899675533</v>
+        <v>-13.96087742314224</v>
       </c>
       <c r="B4">
-        <v>12.178160437408083</v>
+        <v>12.037817539430526</v>
       </c>
       <c r="C4">
         <v>190.54511692961938</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-12.575820443098227</v>
+        <v>-12.705523075796728</v>
       </c>
       <c r="B5">
-        <v>11.776797268920632</v>
+        <v>11.627818790199646</v>
       </c>
       <c r="C5">
         <v>190.54511692961938</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-11.352845823667018</v>
+        <v>-11.489901815351578</v>
       </c>
       <c r="B6">
-        <v>11.326073511314657</v>
+        <v>11.170784960122949</v>
       </c>
       <c r="C6">
         <v>190.54511692961938</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-10.166920311145764</v>
+        <v>-10.309414904469445</v>
       </c>
       <c r="B7">
-        <v>10.831798210855947</v>
+        <v>10.672159924804499</v>
       </c>
       <c r="C7">
         <v>190.54511692961938</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-9.01511363574381</v>
+        <v>-9.1613335768689232</v>
       </c>
       <c r="B8">
-        <v>10.29741592480921</v>
+        <v>10.135173932701376</v>
       </c>
       <c r="C8">
         <v>190.54511692961938</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-7.8928885208696489</v>
+        <v>-8.0414358342307164</v>
       </c>
       <c r="B9">
-        <v>9.728260260712954</v>
+        <v>9.564824884751328</v>
       </c>
       <c r="C9">
         <v>190.54511692961938</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.7953542509785905</v>
+        <v>-6.9451714000312776</v>
       </c>
       <c r="B10">
-        <v>9.1300802966257351</v>
+        <v>8.9664992898025844</v>
       </c>
       <c r="C10">
         <v>190.54511692961938</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.717813361514108</v>
+        <v>-5.8681701169678542</v>
       </c>
       <c r="B11">
-        <v>8.508397942412472</v>
+        <v>8.3453704358646785</v>
       </c>
       <c r="C11">
         <v>190.54511692961938</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.6577390167826387</v>
+        <v>-4.8080797390618439</v>
       </c>
       <c r="B12">
-        <v>7.8661835150974735</v>
+        <v>7.7042228556382915</v>
       </c>
       <c r="C12">
         <v>190.54511692961938</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.6210936455543159</v>
+        <v>-3.7704395464104157</v>
       </c>
       <c r="B13">
-        <v>7.1964281285362066</v>
+        <v>7.0364992814273259</v>
       </c>
       <c r="C13">
         <v>190.54511692961938</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.611430716702567</v>
+        <v>-2.758549840062841</v>
       </c>
       <c r="B14">
-        <v>6.49495464959849</v>
+        <v>6.3382928955446181</v>
       </c>
       <c r="C14">
         <v>190.54511692961938</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.6141785950503389</v>
+        <v>-1.7588634788010675</v>
       </c>
       <c r="B15">
-        <v>5.7788921603804253</v>
+        <v>5.625640480735453</v>
       </c>
       <c r="C15">
         <v>190.54511692961938</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-0.61597237538999106</v>
+        <v>-0.75895521792204057</v>
       </c>
       <c r="B16">
-        <v>5.0639512215518883</v>
+        <v>4.91325074540205</v>
       </c>
       <c r="C16">
         <v>190.54511692961938</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>0.37360082355799717</v>
+        <v>0.23226515895000435</v>
       </c>
       <c r="B17">
-        <v>4.3388620928515413</v>
+        <v>4.1905765001418791</v>
       </c>
       <c r="C17">
         <v>190.54511692961938</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>1.342150751826485</v>
+        <v>1.2032820057750617</v>
       </c>
       <c r="B18">
-        <v>3.5890599292019827</v>
+        <v>3.4439857977608805</v>
       </c>
       <c r="C18">
         <v>190.54511692961938</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>2.2890266583898748</v>
+        <v>2.1534912551774292</v>
       </c>
       <c r="B19">
-        <v>2.8137797671927149</v>
+        <v>2.6727635577035516</v>
       </c>
       <c r="C19">
         <v>190.54511692961938</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>3.21651266695796</v>
+        <v>3.0850167344474846</v>
       </c>
       <c r="B20">
-        <v>2.0157066138299573</v>
+        <v>1.8794239160740247</v>
       </c>
       <c r="C20">
         <v>190.54511692961938</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.1268929012405167</v>
+        <v>3.9999822708755866</v>
       </c>
       <c r="B21">
-        <v>1.1975254761199476</v>
+        <v>1.0664810089764483</v>
       </c>
       <c r="C21">
         <v>190.54511692961938</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>5.022043571045633</v>
+        <v>4.900132307601095</v>
       </c>
       <c r="B22">
-        <v>0.36144185477976531</v>
+        <v>0.23599986660331143</v>
       </c>
       <c r="C22">
         <v>190.54511692961938</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>5.9022092305745613</v>
+        <v>5.7856937511592852</v>
       </c>
       <c r="B23">
-        <v>-0.49225677463006923</v>
+        <v>-0.61175090449946434</v>
       </c>
       <c r="C23">
         <v>190.54511692961938</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>6.7672265201268456</v>
+        <v>6.65651412393441</v>
       </c>
       <c r="B24">
-        <v>-1.3637624428381725</v>
+        <v>-1.4769518036975953</v>
       </c>
       <c r="C24">
         <v>190.54511692961938</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>7.6169320800020373</v>
+        <v>7.512440948310724</v>
       </c>
       <c r="B25">
-        <v>-2.2532671805731646</v>
+        <v>-2.3597833303568057</v>
       </c>
       <c r="C25">
         <v>190.54511692961938</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>8.4510929195076834</v>
+        <v>8.35325681285338</v>
       </c>
       <c r="B26">
-        <v>-3.1610448703918115</v>
+        <v>-3.26050285094954</v>
       </c>
       <c r="C26">
         <v>190.54511692961938</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>9.26919752398336</v>
+        <v>9.1784845708511114</v>
       </c>
       <c r="B27">
-        <v>-4.0876968021634816</v>
+        <v>-4.1796752003751463</v>
       </c>
       <c r="C27">
         <v>190.54511692961938</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>10.070664747776618</v>
+        <v>9.9875821417735331</v>
       </c>
       <c r="B28">
-        <v>-5.0339061175856719</v>
+        <v>-5.1179420806396863</v>
       </c>
       <c r="C28">
         <v>190.54511692961938</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>10.85491344523504</v>
+        <v>10.780007445090273</v>
       </c>
       <c r="B29">
-        <v>-6.000355958355895</v>
+        <v>-6.0759451937492353</v>
       </c>
       <c r="C29">
         <v>190.54511692961938</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>11.621661078038537</v>
+        <v>11.555495744731163</v>
       </c>
       <c r="B30">
-        <v>-6.9873784506920451</v>
+        <v>-7.0539979279510714</v>
       </c>
       <c r="C30">
         <v>190.54511692961938</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>12.371819537196442</v>
+        <v>12.31489168246689</v>
       </c>
       <c r="B31">
-        <v>-7.9939016588935816</v>
+        <v>-8.051100416457361</v>
       </c>
       <c r="C31">
         <v>190.54511692961938</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>13.106599321050448</v>
+        <v>13.059317244528359</v>
       </c>
       <c r="B32">
-        <v>-9.0185026317803612</v>
+        <v>-9.0659244787214917</v>
       </c>
       <c r="C32">
         <v>190.54511692961938</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>13.827210927942231</v>
+        <v>13.78989441714646</v>
       </c>
       <c r="B33">
-        <v>-10.05975841817223</v>
+        <v>-10.097141934196834</v>
       </c>
       <c r="C33">
         <v>190.54511692961938</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>14.534373845565677</v>
+        <v>14.507288523575138</v>
       </c>
       <c r="B34">
-        <v>-11.116823254115717</v>
+        <v>-11.143965189079857</v>
       </c>
       <c r="C34">
         <v>190.54511692961938</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>15.226843519023506</v>
+        <v>15.210338235160553</v>
       </c>
       <c r="B35">
-        <v>-12.191160124564121</v>
+        <v>-12.207768996539361</v>
       </c>
       <c r="C35">
         <v>190.54511692961938</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>15.902884382770626</v>
+        <v>15.897425560271895</v>
       </c>
       <c r="B36">
-        <v>-13.284809201697392</v>
+        <v>-13.290468696487222</v>
       </c>
       <c r="C36">
         <v>190.54511692961938</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>16.560760871261955</v>
+        <v>16.566932507278363</v>
       </c>
       <c r="B37">
-        <v>-14.399810657695518</v>
+        <v>-14.393979628835332</v>
       </c>
       <c r="C37">
         <v>190.54511692961938</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>17.197538364011979</v>
+        <v>17.216126270854176</v>
       </c>
       <c r="B38">
-        <v>-15.539614164102336</v>
+        <v>-15.521536823365212</v>
       </c>
       <c r="C38">
         <v>190.54511692961938</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>17.80548602077339</v>
+        <v>17.837814790893596</v>
       </c>
       <c r="B39">
-        <v>-16.713307389917158</v>
+        <v>-16.681654069336908</v>
       </c>
       <c r="C39">
         <v>190.54511692961938</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>18.375673946358443</v>
+        <v>18.4236911935959</v>
       </c>
       <c r="B40">
-        <v>-17.931387503503153</v>
+        <v>-17.884164845880107</v>
       </c>
       <c r="C40">
         <v>190.54511692961938</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>18.899172245579404</v>
+        <v>18.965448605160375</v>
       </c>
       <c r="B41">
-        <v>-19.204351673223513</v>
+        <v>-19.138902632124495</v>
       </c>
       <c r="C41">
         <v>190.54511692961938</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>18.899172245579404</v>
+        <v>18.965448605160375</v>
       </c>
       <c r="B42">
-        <v>-19.204351673223513</v>
+        <v>-19.138902632124495</v>
       </c>
       <c r="C42">
         <v>190.54511692961938</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>17.958126247233238</v>
+        <v>18.035566015025594</v>
       </c>
       <c r="B43">
-        <v>-18.422218404115952</v>
+        <v>-18.343618177510972</v>
       </c>
       <c r="C43">
         <v>190.54511692961938</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>17.042101137557651</v>
+        <v>17.128221863578393</v>
       </c>
       <c r="B44">
-        <v>-17.610672865832822</v>
+        <v>-17.52165325660328</v>
       </c>
       <c r="C44">
         <v>190.54511692961938</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>16.142354508777807</v>
+        <v>16.235296001413598</v>
       </c>
       <c r="B45">
-        <v>-16.779991833675791</v>
+        <v>-16.68262030864404</v>
       </c>
       <c r="C45">
         <v>190.54511692961938</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>15.250143953118879</v>
+        <v>15.348668279126043</v>
       </c>
       <c r="B46">
-        <v>-15.940452082946546</v>
+        <v>-15.836131772875902</v>
       </c>
       <c r="C46">
         <v>190.54511692961938</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>14.357918580354141</v>
+        <v>14.461325854288107</v>
       </c>
       <c r="B47">
-        <v>-15.100929749852249</v>
+        <v>-14.990489284944987</v>
       </c>
       <c r="C47">
         <v>190.54511692961938</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>13.462893570449181</v>
+        <v>13.570685112382364</v>
       </c>
       <c r="B48">
-        <v>-14.264698414221959</v>
+        <v>-14.148751266111288</v>
       </c>
       <c r="C48">
         <v>190.54511692961938</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>12.563475620917691</v>
+        <v>12.675269745868933</v>
       </c>
       <c r="B49">
-        <v>-13.433631016790203</v>
+        <v>-13.31266533403827</v>
       </c>
       <c r="C49">
         <v>190.54511692961938</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>11.658071429273376</v>
+        <v>11.773603447207954</v>
       </c>
       <c r="B50">
-        <v>-12.609600498291524</v>
+        <v>-12.483979106389416</v>
       </c>
       <c r="C50">
         <v>190.54511692961938</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>10.7455711302487</v>
+        <v>10.864659029229056</v>
       </c>
       <c r="B51">
-        <v>-11.793911514864504</v>
+        <v>-11.663908542843922</v>
       </c>
       <c r="C51">
         <v>190.54511692961938</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>9.8267986074513072</v>
+        <v>9.94920578623998</v>
       </c>
       <c r="B52">
-        <v>-10.985595584263923</v>
+        <v>-10.851542971143955</v>
       </c>
       <c r="C52">
         <v>190.54511692961938</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>8.9030611817076242</v>
+        <v>9.028462132917987</v>
       </c>
       <c r="B53">
-        <v>-10.183115939648612</v>
+        <v>-10.045440061047426</v>
       </c>
       <c r="C53">
         <v>190.54511692961938</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>7.9756661738440666</v>
+        <v>8.10364648394032</v>
       </c>
       <c r="B54">
-        <v>-9.3849358141774</v>
+        <v>-9.244157482312227</v>
       </c>
       <c r="C54">
         <v>190.54511692961938</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>7.04561562547882</v>
+        <v>7.1756932648006631</v>
       </c>
       <c r="B55">
-        <v>-8.58987729933603</v>
+        <v>-8.4465890843201041</v>
       </c>
       <c r="C55">
         <v>190.54511692961938</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>6.1126904613971442</v>
+        <v>6.2444009442584472</v>
       </c>
       <c r="B56">
-        <v>-7.798197919917917</v>
+        <v>-7.6529734349481906</v>
       </c>
       <c r="C56">
         <v>190.54511692961938</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5.1763663271760434</v>
+        <v>5.3092840018895133</v>
       </c>
       <c r="B57">
-        <v>-7.0105140590433876</v>
+        <v>-6.8638852816974589</v>
       </c>
       <c r="C57">
         <v>190.54511692961938</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4.2361188683925457</v>
+        <v>4.3698569172697272</v>
       </c>
       <c r="B58">
-        <v>-6.22744209983278</v>
+        <v>-6.07989937206889</v>
       </c>
       <c r="C58">
         <v>190.54511692961938</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.2914870545894166</v>
+        <v>3.4256928224354968</v>
       </c>
       <c r="B59">
-        <v>-5.4495239875416956</v>
+        <v>-5.3015210221791946</v>
       </c>
       <c r="C59">
         <v>190.54511692961938</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.3422631511724519</v>
+        <v>2.4765994592654974</v>
       </c>
       <c r="B60">
-        <v>-4.6770039159668571</v>
+        <v>-4.5289778226080459</v>
       </c>
       <c r="C60">
         <v>190.54511692961938</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.3883027475132017</v>
+        <v>1.5224432220989668</v>
       </c>
       <c r="B61">
-        <v>-3.9100516410402646</v>
+        <v>-3.7624279325508558</v>
       </c>
       <c r="C61">
         <v>190.54511692961938</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.42946143298322015</v>
+        <v>0.56309050527514448</v>
       </c>
       <c r="B62">
-        <v>-3.1488369186939233</v>
+        <v>-3.0020295112030433</v>
       </c>
       <c r="C62">
         <v>190.54511692961938</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.53400373308391669</v>
+        <v>-0.40121933043049857</v>
       </c>
       <c r="B63">
-        <v>-2.3930575734770434</v>
+        <v>-2.2474992089861114</v>
       </c>
       <c r="C63">
         <v>190.54511692961938</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.5002298115065482</v>
+        <v>-1.3687550584975738</v>
       </c>
       <c r="B64">
-        <v>-1.6405237044076666</v>
+        <v>-1.4967876412259289</v>
       </c>
       <c r="C64">
         <v>190.54511692961938</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.4669523931409718</v>
+        <v>-2.3374124859694416</v>
       </c>
       <c r="B65">
-        <v>-0.88857347912106321</v>
+        <v>-0.7474039144744713</v>
       </c>
       <c r="C65">
         <v>190.54511692961938</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.4319070688435023</v>
+        <v>-3.30508741988948</v>
       </c>
       <c r="B66">
-        <v>-0.13454506525248441</v>
+        <v>0.0031428647163007657</v>
       </c>
       <c r="C66">
         <v>190.54511692961938</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-4.3957695445393217</v>
+        <v>-4.2724087809740432</v>
       </c>
       <c r="B67">
-        <v>0.62076723908913167</v>
+        <v>0.75410819499884685</v>
       </c>
       <c r="C67">
         <v>190.54511692961938</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-5.3709759864290989</v>
+        <v>-5.2509379446314064</v>
       </c>
       <c r="B68">
-        <v>1.3627446139001302</v>
+        <v>1.4918059958433216</v>
       </c>
       <c r="C68">
         <v>190.54511692961938</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-6.3671670793896444</v>
+        <v>-6.2496380426439968</v>
       </c>
       <c r="B69">
-        <v>2.0800543514431316</v>
+        <v>2.205625925569636</v>
       </c>
       <c r="C69">
         <v>190.54511692961938</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-7.3710411227267532</v>
+        <v>-7.2561467775988424</v>
       </c>
       <c r="B70">
-        <v>2.7883327149404997</v>
+        <v>2.9102021770789617</v>
       </c>
       <c r="C70">
         <v>190.54511692961938</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-8.3680956752403421</v>
+        <v>-8.2569859206561915</v>
       </c>
       <c r="B71">
-        <v>3.5046274483751034</v>
+        <v>3.6214899562863567</v>
       </c>
       <c r="C71">
         <v>190.54511692961938</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-9.3619677192777839</v>
+        <v>-9.2555389464645437</v>
       </c>
       <c r="B72">
-        <v>4.2246632478120567</v>
+        <v>4.3354839865811456</v>
       </c>
       <c r="C72">
         <v>190.54511692961938</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-10.358710226585041</v>
+        <v>-10.257435309614229</v>
       </c>
       <c r="B73">
-        <v>4.9413247930623578</v>
+        <v>5.0455202538524171</v>
       </c>
       <c r="C73">
         <v>190.54511692961938</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-11.355900702955012</v>
+        <v>-11.260426680974648</v>
       </c>
       <c r="B74">
-        <v>5.657459746838291</v>
+        <v>5.75426027651405</v>
       </c>
       <c r="C74">
         <v>190.54511692961938</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-12.348953132382606</v>
+        <v>-12.260253898232417</v>
       </c>
       <c r="B75">
-        <v>6.3784590102769583</v>
+        <v>6.4667459493538377</v>
       </c>
       <c r="C75">
         <v>190.54511692961938</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-13.333102877623814</v>
+        <v>-13.252492250063897</v>
       </c>
       <c r="B76">
-        <v>7.109923455313397</v>
+        <v>7.1882151401304171</v>
       </c>
       <c r="C76">
         <v>190.54511692961938</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-14.303946441363539</v>
+        <v>-14.233052972984813</v>
       </c>
       <c r="B77">
-        <v>7.8570294307995816</v>
+        <v>7.92350802956079</v>
       </c>
       <c r="C77">
         <v>190.54511692961938</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-15.258703507241282</v>
+        <v>-15.199356643878565</v>
       </c>
       <c r="B78">
-        <v>8.6230452224572947</v>
+        <v>8.6756780772246138</v>
       </c>
       <c r="C78">
         <v>190.54511692961938</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-16.192589777179659</v>
+        <v>-16.146961316865042</v>
       </c>
       <c r="B79">
-        <v>9.4135948136997936</v>
+        <v>9.4499835527375176</v>
       </c>
       <c r="C79">
         <v>190.54511692961938</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-17.097164619177061</v>
+        <v>-17.068026865037908</v>
       </c>
       <c r="B80">
-        <v>10.238600239819737</v>
+        <v>10.255705411385105</v>
       </c>
       <c r="C80">
         <v>190.54511692961938</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-17.951590271483667</v>
+        <v>-17.943190004295914</v>
       </c>
       <c r="B81">
-        <v>11.122556468428851</v>
+        <v>11.11576544717312</v>
       </c>
       <c r="C81">
         <v>190.54511692961938</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-18.379220738620816</v>
+        <v>-18.422351711139434</v>
       </c>
       <c r="B82">
-        <v>12.508214096788983</v>
+        <v>12.44460253608519</v>
       </c>
       <c r="C82">
         <v>190.54511692961938</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-23.877680056384193</v>
+        <v>-23.847538482223566</v>
       </c>
       <c r="B1">
-        <v>9.5284949956057741</v>
+        <v>9.603683152582537</v>
       </c>
       <c r="C1">
         <v>230.80559063164714</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-22.311722955619231</v>
+        <v>-22.341048587129386</v>
       </c>
       <c r="B2">
-        <v>9.5490584775968355</v>
+        <v>9.4868581735417283</v>
       </c>
       <c r="C2">
         <v>230.80559063164714</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-20.881623998918116</v>
+        <v>-20.934375251476311</v>
       </c>
       <c r="B3">
-        <v>9.2647425982843661</v>
+        <v>9.1479198325991291</v>
       </c>
       <c r="C3">
         <v>230.80559063164714</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-19.472778368600839</v>
+        <v>-19.543957375097936</v>
       </c>
       <c r="B4">
-        <v>8.93273211355731</v>
+        <v>8.7728095906315051</v>
       </c>
       <c r="C4">
         <v>230.80559063164714</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-18.078816168384691</v>
+        <v>-18.165149691755545</v>
       </c>
       <c r="B5">
-        <v>8.5673217123622045</v>
+        <v>8.3718641663856079</v>
       </c>
       <c r="C5">
         <v>230.80559063164714</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-16.697140607894692</v>
+        <v>-16.796058014630731</v>
       </c>
       <c r="B6">
-        <v>8.1743388538949358</v>
+        <v>7.9492985338563535</v>
       </c>
       <c r="C6">
         <v>230.80559063164714</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-15.326269669458018</v>
+        <v>-15.435601018109491</v>
       </c>
       <c r="B7">
-        <v>7.7571093351082245</v>
+        <v>7.5075188756328837</v>
       </c>
       <c r="C7">
         <v>230.80559063164714</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-13.965332174369493</v>
+        <v>-14.083142780506309</v>
       </c>
       <c r="B8">
-        <v>7.317588168776985</v>
+        <v>7.0479402545491645</v>
       </c>
       <c r="C8">
         <v>230.80559063164714</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-12.612965902726032</v>
+        <v>-12.737689424148842</v>
       </c>
       <c r="B9">
-        <v>6.8588323135904732</v>
+        <v>6.5727742626732475</v>
       </c>
       <c r="C9">
         <v>230.80559063164714</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-11.267700074320599</v>
+        <v>-11.398167952512941</v>
       </c>
       <c r="B10">
-        <v>6.3841423484961739</v>
+        <v>6.0844085485739088</v>
       </c>
       <c r="C10">
         <v>230.80559063164714</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-9.9281207089281285</v>
+        <v>-10.063546849653934</v>
       </c>
       <c r="B11">
-        <v>5.8966913875601126</v>
+        <v>5.5851384575887186</v>
       </c>
       <c r="C11">
         <v>230.80559063164714</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-8.59347314418532</v>
+        <v>-8.7332753517260588</v>
       </c>
       <c r="B12">
-        <v>5.39817296914841</v>
+        <v>5.07618955800095</v>
       </c>
       <c r="C12">
         <v>230.80559063164714</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-7.2655831891939684</v>
+        <v>-7.40868422269967</v>
       </c>
       <c r="B13">
-        <v>4.8844897937090037</v>
+        <v>4.5546006131079082</v>
       </c>
       <c r="C13">
         <v>230.80559063164714</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-5.9455429293353674</v>
+        <v>-6.0905692911535763</v>
       </c>
       <c r="B14">
-        <v>4.3531911116322179</v>
+        <v>4.0186007327674655</v>
       </c>
       <c r="C14">
         <v>230.80559063164714</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-4.6289290836436807</v>
+        <v>-4.7757051162842465</v>
       </c>
       <c r="B15">
-        <v>3.814203210996101</v>
+        <v>3.4753672180657071</v>
       </c>
       <c r="C15">
         <v>230.80559063164714</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.3116846405089064</v>
+        <v>-3.4611333398422524</v>
       </c>
       <c r="B16">
-        <v>3.27663043454716</v>
+        <v>2.9314830538317165</v>
       </c>
       <c r="C16">
         <v>230.80559063164714</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.9967330320913999</v>
+        <v>-2.1489852031768426</v>
       </c>
       <c r="B17">
-        <v>2.7339123060179711</v>
+        <v>2.3822057686383173</v>
       </c>
       <c r="C17">
         <v>230.80559063164714</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.68784934806113351</v>
+        <v>-0.84201294382946823</v>
       </c>
       <c r="B18">
-        <v>2.1775771438956446</v>
+        <v>1.8214110406645179</v>
       </c>
       <c r="C18">
         <v>230.80559063164714</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.614765135643918</v>
+        <v>0.45963681548838931</v>
       </c>
       <c r="B19">
-        <v>1.6071732646993076</v>
+        <v>1.2487726027702708</v>
       </c>
       <c r="C19">
         <v>230.80559063164714</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.911802596518783</v>
+        <v>1.7564688557727455</v>
       </c>
       <c r="B20">
-        <v>1.0242539844560918</v>
+        <v>0.66541370148576218</v>
       </c>
       <c r="C20">
         <v>230.80559063164714</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3.203955212058478</v>
+        <v>3.0489879580196022</v>
       </c>
       <c r="B21">
-        <v>0.43037261919313496</v>
+        <v>0.072457583341184337</v>
       </c>
       <c r="C21">
         <v>230.80559063164714</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>4.4917919354257263</v>
+        <v>4.337609024571873</v>
       </c>
       <c r="B22">
-        <v>-0.1731940428774468</v>
+        <v>-0.52917250451128894</v>
       </c>
       <c r="C22">
         <v>230.80559063164714</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>5.77538882245403</v>
+        <v>5.6223874431600551</v>
       </c>
       <c r="B23">
-        <v>-0.78627532480358886</v>
+        <v>-1.1393533124315343</v>
       </c>
       <c r="C23">
         <v>230.80559063164714</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>7.054698704644589</v>
+        <v>6.9032887228615492</v>
       </c>
       <c r="B24">
-        <v>-1.4089770774482433</v>
+        <v>-1.7581615901574437</v>
       </c>
       <c r="C24">
         <v>230.80559063164714</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>8.3296744134985961</v>
+        <v>8.180278372753742</v>
       </c>
       <c r="B25">
-        <v>-2.0414051516743563</v>
+        <v>-2.3856740874269042</v>
       </c>
       <c r="C25">
         <v>230.80559063164714</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>9.60024844149096</v>
+        <v>9.4533070397903867</v>
       </c>
       <c r="B26">
-        <v>-2.6837110411687837</v>
+        <v>-3.0220006254067164</v>
       </c>
       <c r="C26">
         <v>230.80559063164714</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>10.866271924991429</v>
+        <v>10.722265922430628</v>
       </c>
       <c r="B27">
-        <v>-3.33622881091399</v>
+        <v>-3.6673833109792975</v>
       </c>
       <c r="C27">
         <v>230.80559063164714</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>12.127575661343458</v>
+        <v>11.987031357009958</v>
       </c>
       <c r="B28">
-        <v>-3.9993381687163403</v>
+        <v>-4.322097322455976</v>
       </c>
       <c r="C28">
         <v>230.80559063164714</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>13.383990447890488</v>
+        <v>13.247479679863863</v>
       </c>
       <c r="B29">
-        <v>-4.673418822382196</v>
+        <v>-4.9864178381480713</v>
       </c>
       <c r="C29">
         <v>230.80559063164714</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>14.635438810963491</v>
+        <v>14.503554075408017</v>
       </c>
       <c r="B30">
-        <v>-5.3586446306294047</v>
+        <v>-5.66047128497828</v>
       </c>
       <c r="C30">
         <v>230.80559063164714</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>15.882210192843425</v>
+        <v>15.755465120378794</v>
       </c>
       <c r="B31">
-        <v>-6.0543660558217134</v>
+        <v>-6.34378908431476</v>
       </c>
       <c r="C31">
         <v>230.80559063164714</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>17.124685764798805</v>
+        <v>17.003490239592779</v>
       </c>
       <c r="B32">
-        <v>-6.7597277112343646</v>
+        <v>-7.0357539061370584</v>
       </c>
       <c r="C32">
         <v>230.80559063164714</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>18.363246698098106</v>
+        <v>18.247906857866539</v>
       </c>
       <c r="B33">
-        <v>-7.4738742101425872</v>
+        <v>-7.7357484204247031</v>
       </c>
       <c r="C33">
         <v>230.80559063164714</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>19.598125832556335</v>
+        <v>19.488884214850785</v>
       </c>
       <c r="B34">
-        <v>-8.1962830365457648</v>
+        <v>-8.4433960324723518</v>
       </c>
       <c r="C34">
         <v>230.80559063164714</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>20.828962682174609</v>
+        <v>20.726158809532912</v>
       </c>
       <c r="B35">
-        <v>-8.9277631573399177</v>
+        <v>-9.1592830888351831</v>
       </c>
       <c r="C35">
         <v>230.80559063164714</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>22.055248429500537</v>
+        <v>21.959358955734448</v>
       </c>
       <c r="B36">
-        <v>-9.669456410145207</v>
+        <v>-9.8842366713834853</v>
       </c>
       <c r="C36">
         <v>230.80559063164714</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>23.276474257081777</v>
+        <v>23.188112967276968</v>
       </c>
       <c r="B37">
-        <v>-10.422504632581815</v>
+        <v>-10.619083861987571</v>
       </c>
       <c r="C37">
         <v>230.80559063164714</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>24.491767643863721</v>
+        <v>24.411783944955406</v>
       </c>
       <c r="B38">
-        <v>-11.188865849791915</v>
+        <v>-11.365241898673018</v>
       </c>
       <c r="C38">
         <v>230.80559063164714</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>25.698801254382911</v>
+        <v>25.628674137458422</v>
       </c>
       <c r="B39">
-        <v>-11.973762837005753</v>
+        <v>-12.126488644086566</v>
       </c>
       <c r="C39">
         <v>230.80559063164714</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>26.894884049573633</v>
+        <v>26.836820580448073</v>
       </c>
       <c r="B40">
-        <v>-12.783234556975575</v>
+        <v>-12.907192117030233</v>
       </c>
       <c r="C40">
         <v>230.80559063164714</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>28.077324990370204</v>
+        <v>28.034260309586429</v>
       </c>
       <c r="B41">
-        <v>-13.623319972453636</v>
+        <v>-13.711720336306046</v>
       </c>
       <c r="C41">
         <v>230.80559063164714</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>28.077324990370204</v>
+        <v>28.034260309586429</v>
       </c>
       <c r="B42">
-        <v>-13.623319972453636</v>
+        <v>-13.711720336306046</v>
       </c>
       <c r="C42">
         <v>230.80559063164714</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>26.767870949826978</v>
+        <v>26.74421333340111</v>
       </c>
       <c r="B43">
-        <v>-13.068264747802754</v>
+        <v>-13.113263204766019</v>
       </c>
       <c r="C43">
         <v>230.80559063164714</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>25.466588550253274</v>
+        <v>25.459364205635087</v>
       </c>
       <c r="B44">
-        <v>-12.494871537624697</v>
+        <v>-12.503239740009027</v>
       </c>
       <c r="C44">
         <v>230.80559063164714</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>24.170793123978431</v>
+        <v>24.177756378365132</v>
       </c>
       <c r="B45">
-        <v>-11.909165006619432</v>
+        <v>-11.886003682931214</v>
       </c>
       <c r="C45">
         <v>230.80559063164714</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>22.877800003331792</v>
+        <v>22.897433303668016</v>
       </c>
       <c r="B46">
-        <v>-11.317169819486924</v>
+        <v>-11.265908774428729</v>
       </c>
       <c r="C46">
         <v>230.80559063164714</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>21.585288001078542</v>
+        <v>21.616703421903829</v>
       </c>
       <c r="B47">
-        <v>-10.724094954212937</v>
+        <v>-10.646719099344583</v>
       </c>
       <c r="C47">
         <v>230.80559063164714</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>20.292389851727275</v>
+        <v>20.334935126566052</v>
       </c>
       <c r="B48">
-        <v>-10.131886641926453</v>
+        <v>-10.029840118309309</v>
       </c>
       <c r="C48">
         <v>230.80559063164714</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>18.998601770222415</v>
+        <v>19.051761799431443</v>
       </c>
       <c r="B49">
-        <v>-9.5416754270422413</v>
+        <v>-9.4160876359002845</v>
       </c>
       <c r="C49">
         <v>230.80559063164714</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>17.703419971508414</v>
+        <v>17.766816822276809</v>
       </c>
       <c r="B50">
-        <v>-8.9545918539750886</v>
+        <v>-8.8062774566949109</v>
       </c>
       <c r="C50">
         <v>230.80559063164714</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>16.406488754657811</v>
+        <v>16.479841512971827</v>
       </c>
       <c r="B51">
-        <v>-8.3714341514386437</v>
+        <v>-8.20098520419644</v>
       </c>
       <c r="C51">
         <v>230.80559063164714</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>15.108044755255609</v>
+        <v>15.191008933757756</v>
       </c>
       <c r="B52">
-        <v>-7.7916712853420922</v>
+        <v>-7.5998257776115885</v>
       </c>
       <c r="C52">
         <v>230.80559063164714</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>13.808472693014915</v>
+        <v>13.900600082968763</v>
       </c>
       <c r="B53">
-        <v>-7.2144399058934994</v>
+        <v>-7.0021738950729375</v>
       </c>
       <c r="C53">
         <v>230.80559063164714</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>12.508157287648803</v>
+        <v>12.608895958938971</v>
       </c>
       <c r="B54">
-        <v>-6.6388766633009144</v>
+        <v>-6.407404274713052</v>
       </c>
       <c r="C54">
         <v>230.80559063164714</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>11.207391292673909</v>
+        <v>11.3161104730373</v>
       </c>
       <c r="B55">
-        <v>-6.0643245891817674</v>
+        <v>-5.8150409176239339</v>
       </c>
       <c r="C55">
         <v>230.80559063164714</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>9.9060995968209085</v>
+        <v>10.022189188771622</v>
       </c>
       <c r="B56">
-        <v>-5.490952240790933</v>
+        <v>-5.2252049567352357</v>
       </c>
       <c r="C56">
         <v>230.80559063164714</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>8.6041151226240071</v>
+        <v>8.72701058268458</v>
       </c>
       <c r="B57">
-        <v>-4.91913455679266</v>
+        <v>-4.63816680793604</v>
       </c>
       <c r="C57">
         <v>230.80559063164714</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>7.3012707926173963</v>
+        <v>7.4304531313188056</v>
       </c>
       <c r="B58">
-        <v>-4.349246475851186</v>
+        <v>-4.0541968871154168</v>
       </c>
       <c r="C58">
         <v>230.80559063164714</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5.9974196336435934</v>
+        <v>6.1324099369641125</v>
       </c>
       <c r="B59">
-        <v>-3.7816178205376327</v>
+        <v>-3.4735330647221359</v>
       </c>
       <c r="C59">
         <v>230.80559063164714</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4.6924950897783786</v>
+        <v>4.8328326048990391</v>
       </c>
       <c r="B60">
-        <v>-3.2163979490506165</v>
+        <v>-2.8962830294437283</v>
       </c>
       <c r="C60">
         <v>230.80559063164714</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3.3864507094058651</v>
+        <v>3.531687366149324</v>
       </c>
       <c r="B61">
-        <v>-2.6536911034956385</v>
+        <v>-2.3225219245274253</v>
       </c>
       <c r="C61">
         <v>230.80559063164714</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2.0792400409101521</v>
+        <v>2.2289404517406921</v>
       </c>
       <c r="B62">
-        <v>-2.0936015259781939</v>
+        <v>-1.7523248932204534</v>
       </c>
       <c r="C62">
         <v>230.80559063164714</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.77093961339609973</v>
+        <v>0.92464772601909118</v>
       </c>
       <c r="B63">
-        <v>-1.5359574774776252</v>
+        <v>-1.1855676253105842</v>
       </c>
       <c r="C63">
         <v>230.80559063164714</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.53788212114842493</v>
+        <v>-0.38077641338867724</v>
       </c>
       <c r="B64">
-        <v>-0.97948329446865057</v>
+        <v>-0.62132799674776018</v>
       </c>
       <c r="C64">
         <v>230.80559063164714</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.8465337300147884</v>
+        <v>-1.6868279355355831</v>
       </c>
       <c r="B65">
-        <v>-0.42262733229983768</v>
+        <v>-0.058484430022471876</v>
       </c>
       <c r="C65">
         <v>230.80559063164714</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.1543237804943702</v>
+        <v>-2.9930028094746097</v>
       </c>
       <c r="B66">
-        <v>0.13616205368025122</v>
+        <v>0.50408465237479538</v>
       </c>
       <c r="C66">
         <v>230.80559063164714</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-4.4614544892545966</v>
+        <v>-4.2994486052937928</v>
       </c>
       <c r="B67">
-        <v>0.6964310688990899</v>
+        <v>1.0660508751869344</v>
       </c>
       <c r="C67">
         <v>230.80559063164714</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-5.7717026704670937</v>
+        <v>-5.6089192972214024</v>
       </c>
       <c r="B68">
-        <v>1.2497041618883036</v>
+        <v>1.621286052090358</v>
       </c>
       <c r="C68">
         <v>230.80559063164714</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-7.087993763708381</v>
+        <v>-6.9235481482070647</v>
       </c>
       <c r="B69">
-        <v>1.7894163515364228</v>
+        <v>2.1650432131613151</v>
       </c>
       <c r="C69">
         <v>230.80559063164714</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-8.4062731126702559</v>
+        <v>-8.240379171945488</v>
       </c>
       <c r="B70">
-        <v>2.3246666950554138</v>
+        <v>2.7039000651418341</v>
       </c>
       <c r="C70">
         <v>230.80559063164714</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-9.7221200061934159</v>
+        <v>-9.5561895155976835</v>
       </c>
       <c r="B71">
-        <v>2.8653757136186293</v>
+        <v>3.2450281503390563</v>
       </c>
       <c r="C71">
         <v>230.80559063164714</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-11.036629609598814</v>
+        <v>-10.871778109444676</v>
       </c>
       <c r="B72">
-        <v>3.4090857459215123</v>
+        <v>3.786649676654771</v>
       </c>
       <c r="C72">
         <v>230.80559063164714</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-12.351631057321505</v>
+        <v>-12.188479066286579</v>
       </c>
       <c r="B73">
-        <v>3.9516920300291543</v>
+        <v>4.3257959555181706</v>
       </c>
       <c r="C73">
         <v>230.80559063164714</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-13.666373483772734</v>
+        <v>-13.505745445879811</v>
       </c>
       <c r="B74">
-        <v>4.4948795839631481</v>
+        <v>4.863684046873443</v>
       </c>
       <c r="C74">
         <v>230.80559063164714</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-14.979446943563701</v>
+        <v>-14.822549795625738</v>
       </c>
       <c r="B75">
-        <v>5.041812467210482</v>
+        <v>5.4026002542373037</v>
       </c>
       <c r="C75">
         <v>230.80559063164714</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-16.28938517212929</v>
+        <v>-16.137823666549235</v>
       </c>
       <c r="B76">
-        <v>5.5957811251632421</v>
+        <v>5.9449221069016334</v>
       </c>
       <c r="C76">
         <v>230.80559063164714</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-17.594830711092975</v>
+        <v>-17.450577976148992</v>
       </c>
       <c r="B77">
-        <v>6.1598318311654934</v>
+        <v>6.4928505266452854</v>
       </c>
       <c r="C77">
         <v>230.80559063164714</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-18.894917646008782</v>
+        <v>-18.760182104195469</v>
       </c>
       <c r="B78">
-        <v>6.7359077844641124</v>
+        <v>7.0477887794198253</v>
       </c>
       <c r="C78">
         <v>230.80559063164714</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-20.188169451113875</v>
+        <v>-20.065560255789958</v>
       </c>
       <c r="B79">
-        <v>7.3273224576126017</v>
+        <v>7.6121307407806489</v>
       </c>
       <c r="C79">
         <v>230.80559063164714</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-21.471995280603632</v>
+        <v>-21.364824230688171</v>
       </c>
       <c r="B80">
-        <v>7.9398899695921292</v>
+        <v>8.1900780633047336</v>
       </c>
       <c r="C80">
         <v>230.80559063164714</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-22.740031532528331</v>
+        <v>-22.653335101459561</v>
       </c>
       <c r="B81">
-        <v>8.5878908842318786</v>
+        <v>8.7919533605242268</v>
       </c>
       <c r="C81">
         <v>230.80559063164714</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-23.877680056384193</v>
+        <v>-23.847538482223566</v>
       </c>
       <c r="B82">
-        <v>9.5284949956057741</v>
+        <v>9.603683152582537</v>
       </c>
       <c r="C82">
         <v>230.80559063164714</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-27.497292372826667</v>
+        <v>-27.45103866038054</v>
       </c>
       <c r="B1">
-        <v>8.365221884807454</v>
+        <v>8.5157795582710012</v>
       </c>
       <c r="C1">
         <v>265.01886677730067</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-25.851243165560163</v>
+        <v>-25.842758306838487</v>
       </c>
       <c r="B2">
-        <v>8.280215289274615</v>
+        <v>8.31010642657773</v>
       </c>
       <c r="C2">
         <v>265.01886677730067</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-24.274833433081152</v>
+        <v>-24.28210751857771</v>
       </c>
       <c r="B3">
-        <v>7.9827720120716661</v>
+        <v>7.9617839695667936</v>
       </c>
       <c r="C3">
         <v>265.01886677730067</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-22.709199044883817</v>
+        <v>-22.729187970535179</v>
       </c>
       <c r="B4">
-        <v>7.6524583206383516</v>
+        <v>7.5903066465710829</v>
       </c>
       <c r="C4">
         <v>265.01886677730067</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-21.151069368723189</v>
+        <v>-21.181782679596914</v>
       </c>
       <c r="B5">
-        <v>7.2992513473870257</v>
+        <v>7.2023142651047385</v>
       </c>
       <c r="C5">
         <v>265.01886677730067</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-19.599111716397086</v>
+        <v>-19.638988211114754</v>
       </c>
       <c r="B6">
-        <v>6.92721648569175</v>
+        <v>6.8005125887468969</v>
       </c>
       <c r="C6">
         <v>265.01886677730067</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-18.052565903329771</v>
+        <v>-18.100289184272629</v>
       </c>
       <c r="B7">
-        <v>6.5386726945799687</v>
+        <v>6.3864451698113243</v>
       </c>
       <c r="C7">
         <v>265.01886677730067</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-16.510985451859803</v>
+        <v>-16.56538285431694</v>
       </c>
       <c r="B8">
-        <v>6.13498196354292</v>
+        <v>5.9610187210632857</v>
       </c>
       <c r="C8">
         <v>265.01886677730067</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-14.973671571595739</v>
+        <v>-15.033795470107341</v>
       </c>
       <c r="B9">
-        <v>5.7182759673584087</v>
+        <v>5.5256521150064826</v>
       </c>
       <c r="C9">
         <v>265.01886677730067</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-13.439869664886496</v>
+        <v>-13.505015459903342</v>
       </c>
       <c r="B10">
-        <v>5.2908566220227522</v>
+        <v>5.0818774958710566</v>
       </c>
       <c r="C10">
         <v>265.01886677730067</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-11.908854217772589</v>
+        <v>-11.978550975950776</v>
       </c>
       <c r="B11">
-        <v>4.8549371231197886</v>
+        <v>4.6311679350545258</v>
       </c>
       <c r="C11">
         <v>265.01886677730067</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-10.380238322017029</v>
+        <v>-10.454139683295246</v>
       </c>
       <c r="B12">
-        <v>4.411697742359296</v>
+        <v>4.17430911901089</v>
       </c>
       <c r="C12">
         <v>265.01886677730067</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-8.8549604085813183</v>
+        <v>-8.9324175741951937</v>
       </c>
       <c r="B13">
-        <v>3.9582757763672922</v>
+        <v>3.7093962672527083</v>
       </c>
       <c r="C13">
         <v>265.01886677730067</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-7.3335819937424782</v>
+        <v>-7.4137651733947365</v>
       </c>
       <c r="B14">
-        <v>3.4929583079375681</v>
+        <v>3.2352897179398021</v>
       </c>
       <c r="C14">
         <v>265.01886677730067</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-5.8138315958411688</v>
+        <v>-5.8966428083679006</v>
       </c>
       <c r="B15">
-        <v>3.0226745396187633</v>
+        <v>2.756600750762471</v>
       </c>
       <c r="C15">
         <v>265.01886677730067</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-4.2936258226551525</v>
+        <v>-4.3796382987833757</v>
       </c>
       <c r="B16">
-        <v>2.55377990317802</v>
+        <v>2.2775588095609036</v>
       </c>
       <c r="C16">
         <v>265.01886677730067</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.7744666376468845</v>
+        <v>-2.8637696303585178</v>
       </c>
       <c r="B17">
-        <v>2.0816926275016314</v>
+        <v>1.7951150532443363</v>
       </c>
       <c r="C17">
         <v>265.01886677730067</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.258293394699145</v>
+        <v>-1.3503512590920599</v>
       </c>
       <c r="B18">
-        <v>1.600496672804703</v>
+        <v>1.305332719839994</v>
       </c>
       <c r="C18">
         <v>265.01886677730067</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.25479034630870911</v>
+        <v>0.16054664394045046</v>
       </c>
       <c r="B19">
-        <v>1.10987612749843</v>
+        <v>0.808001648777993</v>
       </c>
       <c r="C19">
         <v>265.01886677730067</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.7651399739981861</v>
+        <v>1.669164978894272</v>
       </c>
       <c r="B20">
-        <v>0.61091511204303</v>
+        <v>0.303843329839169</v>
       </c>
       <c r="C20">
         <v>265.01886677730067</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3.2731108769907906</v>
+        <v>3.17574464592466</v>
       </c>
       <c r="B21">
-        <v>0.10469774689872001</v>
+        <v>-0.20642074719564163</v>
       </c>
       <c r="C21">
         <v>265.01886677730067</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>4.7789951970142859</v>
+        <v>4.6804836706944331</v>
       </c>
       <c r="B22">
-        <v>-0.40788478345311735</v>
+        <v>-0.72219750054983312</v>
       </c>
       <c r="C22">
         <v>265.01886677730067</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>6.2828320882214364</v>
+        <v>6.183408580896633</v>
       </c>
       <c r="B23">
-        <v>-0.92671303844643227</v>
+        <v>-1.2434074804637212</v>
       </c>
       <c r="C23">
         <v>265.01886677730067</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>7.7845974578712669</v>
+        <v>7.6845030297318679</v>
       </c>
       <c r="B24">
-        <v>-1.4518605134940086</v>
+        <v>-1.7700996451818536</v>
       </c>
       <c r="C24">
         <v>265.01886677730067</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>9.28426721322279</v>
+        <v>9.1837506704007339</v>
       </c>
       <c r="B25">
-        <v>-1.9834007040086306</v>
+        <v>-2.3023229529487752</v>
       </c>
       <c r="C25">
         <v>265.01886677730067</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>10.781806858801261</v>
+        <v>10.681128099657558</v>
       </c>
       <c r="B26">
-        <v>-2.5214388391611342</v>
+        <v>-2.8401474958845179</v>
       </c>
       <c r="C26">
         <v>265.01886677730067</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>12.277140288196828</v>
+        <v>12.176583688471521</v>
       </c>
       <c r="B27">
-        <v>-3.06620708315456</v>
+        <v>-3.3837279016110453</v>
       </c>
       <c r="C27">
         <v>265.01886677730067</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>13.770180992265852</v>
+        <v>13.670058751365495</v>
       </c>
       <c r="B28">
-        <v>-3.6179693339499939</v>
+        <v>-3.9332399316257982</v>
       </c>
       <c r="C28">
         <v>265.01886677730067</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>15.260842461864696</v>
+        <v>15.161494602862369</v>
       </c>
       <c r="B29">
-        <v>-4.1769894895085216</v>
+        <v>-4.4888593474262191</v>
       </c>
       <c r="C29">
         <v>265.01886677730067</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>16.749085348061531</v>
+        <v>16.650864517236908</v>
       </c>
       <c r="B30">
-        <v>-4.743387584573818</v>
+        <v>-5.0506661918733196</v>
       </c>
       <c r="C30">
         <v>265.01886677730067</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>18.235058942771722</v>
+        <v>18.138269607771367</v>
       </c>
       <c r="B31">
-        <v>-5.3167082010199014</v>
+        <v>-5.6183576332823808</v>
       </c>
       <c r="C31">
         <v>265.01886677730067</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>19.718959698122454</v>
+        <v>19.623842947499909</v>
       </c>
       <c r="B32">
-        <v>-5.8963520575033792</v>
+        <v>-6.1915351213322536</v>
       </c>
       <c r="C32">
         <v>265.01886677730067</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>21.2009840662409</v>
+        <v>21.107717609456682</v>
       </c>
       <c r="B33">
-        <v>-6.4817198726808591</v>
+        <v>-6.7698001057017905</v>
       </c>
       <c r="C33">
         <v>265.01886677730067</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>22.681252357372429</v>
+        <v>22.589975051956571</v>
       </c>
       <c r="B34">
-        <v>-7.0724446376199</v>
+        <v>-7.3529086208290044</v>
       </c>
       <c r="C34">
         <v>265.01886677730067</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>24.159580314235193</v>
+        <v>24.070490274437454</v>
       </c>
       <c r="B35">
-        <v>-7.6690884330318854</v>
+        <v>-7.9412350401885794</v>
       </c>
       <c r="C35">
         <v>265.01886677730067</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>25.635707537665539</v>
+        <v>25.549086661617935</v>
       </c>
       <c r="B36">
-        <v>-8.2724456120391476</v>
+        <v>-8.5353083220143589</v>
       </c>
       <c r="C36">
         <v>265.01886677730067</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>27.109373628499824</v>
+        <v>27.025587598216649</v>
       </c>
       <c r="B37">
-        <v>-8.8833105277640332</v>
+        <v>-9.1356574245401969</v>
       </c>
       <c r="C37">
         <v>265.01886677730067</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>28.580131417975132</v>
+        <v>28.499689871258568</v>
       </c>
       <c r="B38">
-        <v>-9.5030472779173447</v>
+        <v>-9.743190462842465</v>
       </c>
       <c r="C38">
         <v>265.01886677730067</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>30.0467866589315</v>
+        <v>29.970583876994166</v>
       </c>
       <c r="B39">
-        <v>-10.135298938563796</v>
+        <v>-10.360332179367662</v>
       </c>
       <c r="C39">
         <v>265.01886677730067</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>31.507958334609697</v>
+        <v>31.43733341398028</v>
       </c>
       <c r="B40">
-        <v>-10.784278330356564</v>
+        <v>-10.989886473404802</v>
       </c>
       <c r="C40">
         <v>265.01886677730067</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>32.962265428250483</v>
+        <v>32.899002280773743</v>
       </c>
       <c r="B41">
-        <v>-11.454198273948837</v>
+        <v>-11.634657244242911</v>
       </c>
       <c r="C41">
         <v>265.01886677730067</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>32.962265428250483</v>
+        <v>32.899002280773743</v>
       </c>
       <c r="B42">
-        <v>-11.454198273948837</v>
+        <v>-11.634657244242911</v>
       </c>
       <c r="C42">
         <v>265.01886677730067</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>31.442719579211438</v>
+        <v>31.393114514631485</v>
       </c>
       <c r="B43">
-        <v>-10.983290525026087</v>
+        <v>-11.122320941809958</v>
       </c>
       <c r="C43">
         <v>265.01886677730067</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>29.927513388416106</v>
+        <v>29.88974032454248</v>
       </c>
       <c r="B44">
-        <v>-10.499144557410677</v>
+        <v>-10.602456543623571</v>
       </c>
       <c r="C44">
         <v>265.01886677730067</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>28.415266705330232</v>
+        <v>28.387944389755905</v>
       </c>
       <c r="B45">
-        <v>-10.005970549318326</v>
+        <v>-10.077865311321842</v>
       </c>
       <c r="C45">
         <v>265.01886677730067</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>26.904599379419555</v>
+        <v>26.886791389520937</v>
       </c>
       <c r="B46">
-        <v>-9.5079786789647631</v>
+        <v>-9.5513485065428654</v>
       </c>
       <c r="C46">
         <v>265.01886677730067</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>25.394317999910466</v>
+        <v>25.385472570443408</v>
       </c>
       <c r="B47">
-        <v>-9.0088094710004913</v>
+        <v>-9.0253283249405865</v>
       </c>
       <c r="C47">
         <v>265.01886677730067</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>23.883976115072056</v>
+        <v>23.883685448555912</v>
       </c>
       <c r="B48">
-        <v>-8.509824835815186</v>
+        <v>-8.5007106982323641</v>
       </c>
       <c r="C48">
         <v>265.01886677730067</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>22.373314012934035</v>
+        <v>22.381254107247695</v>
       </c>
       <c r="B49">
-        <v>-8.0118170302332956</v>
+        <v>-7.9780224921514131</v>
       </c>
       <c r="C49">
         <v>265.01886677730067</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>20.862071981526167</v>
+        <v>20.878002629908025</v>
       </c>
       <c r="B50">
-        <v>-7.5155783110792784</v>
+        <v>-7.45779057243095</v>
       </c>
       <c r="C50">
         <v>265.01886677730067</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>19.350066417304912</v>
+        <v>19.373806680631564</v>
       </c>
       <c r="B51">
-        <v>-7.0216687648220644</v>
+        <v>-6.9403873219155843</v>
       </c>
       <c r="C51">
         <v>265.01886677730067</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>17.837418150433624</v>
+        <v>17.868748246334686</v>
       </c>
       <c r="B52">
-        <v>-6.5297197965084779</v>
+        <v>-6.4255671918955288</v>
       </c>
       <c r="C52">
         <v>265.01886677730067</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>16.324324119502382</v>
+        <v>16.362960894639151</v>
       </c>
       <c r="B53">
-        <v>-6.0391306408298151</v>
+        <v>-5.9129301507723886</v>
       </c>
       <c r="C53">
         <v>265.01886677730067</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>14.810981263101246</v>
+        <v>14.85657819316673</v>
       </c>
       <c r="B54">
-        <v>-5.54930053247737</v>
+        <v>-5.402076166947765</v>
       </c>
       <c r="C54">
         <v>265.01886677730067</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>13.297539327203936</v>
+        <v>13.349701716841542</v>
       </c>
       <c r="B55">
-        <v>-5.0597726682106812</v>
+        <v>-4.8927010261314656</v>
       </c>
       <c r="C55">
         <v>265.01886677730067</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>11.783959287318661</v>
+        <v>11.842305069797082</v>
       </c>
       <c r="B56">
-        <v>-4.5706660930622309</v>
+        <v>-4.38488378326608</v>
       </c>
       <c r="C56">
         <v>265.01886677730067</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>10.270154926337273</v>
+        <v>10.334329863469176</v>
       </c>
       <c r="B57">
-        <v>-4.0822438141327426</v>
+        <v>-3.8787993106023957</v>
       </c>
       <c r="C57">
         <v>265.01886677730067</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>8.7560400271516166</v>
+        <v>8.8257177092936665</v>
       </c>
       <c r="B58">
-        <v>-3.5947688385229384</v>
+        <v>-3.3746224803912042</v>
       </c>
       <c r="C58">
         <v>265.01886677730067</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>7.2415387431535407</v>
+        <v>7.3164172423805374</v>
       </c>
       <c r="B59">
-        <v>-3.10847253790529</v>
+        <v>-2.8725071291594939</v>
       </c>
       <c r="C59">
         <v>265.01886677730067</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5.7266167097348939</v>
+        <v>5.8064051925363973</v>
       </c>
       <c r="B60">
-        <v>-2.6234597422392749</v>
+        <v>-2.3725229505390719</v>
       </c>
       <c r="C60">
         <v>265.01886677730067</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4.2112499327875472</v>
+        <v>4.2956653132420293</v>
       </c>
       <c r="B61">
-        <v>-2.1398036460561269</v>
+        <v>-1.8747186024379536</v>
       </c>
       <c r="C61">
         <v>265.01886677730067</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2.6954144182033626</v>
+        <v>2.78418135797821</v>
       </c>
       <c r="B62">
-        <v>-1.6575774438870767</v>
+        <v>-1.3791427427641509</v>
       </c>
       <c r="C62">
         <v>265.01886677730067</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.1791493852531907</v>
+        <v>1.2719799206436435</v>
       </c>
       <c r="B63">
-        <v>-1.1766614965220164</v>
+        <v>-0.88571572347374639</v>
       </c>
       <c r="C63">
         <v>265.01886677730067</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.33725309327619574</v>
+        <v>-0.24074104319126749</v>
       </c>
       <c r="B64">
-        <v>-0.69616482978547256</v>
+        <v>-0.3938446727150951</v>
       </c>
       <c r="C64">
         <v>265.01886677730067</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.8534377312190362</v>
+        <v>-1.7537407375381904</v>
       </c>
       <c r="B65">
-        <v>-0.21500363576063269</v>
+        <v>0.097191587315378566</v>
       </c>
       <c r="C65">
         <v>265.01886677730067</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.3690492424095733</v>
+        <v>-3.2667783664087962</v>
       </c>
       <c r="B66">
-        <v>0.26790589346931692</v>
+        <v>0.58811423442125088</v>
       </c>
       <c r="C66">
         <v>265.01886677730067</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-4.8841913161060679</v>
+        <v>-4.7799242324183737</v>
       </c>
       <c r="B67">
-        <v>0.752247451642471</v>
+        <v>1.0787127140744492</v>
       </c>
       <c r="C67">
         <v>265.01886677730067</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-6.4008035432628958</v>
+        <v>-6.2944930325967352</v>
       </c>
       <c r="B68">
-        <v>1.2321042757820617</v>
+        <v>1.565049542420321</v>
       </c>
       <c r="C68">
         <v>265.01886677730067</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-7.920388163238874</v>
+        <v>-7.8115030331655175</v>
       </c>
       <c r="B69">
-        <v>1.7028937531467598</v>
+        <v>2.0440750382650119</v>
       </c>
       <c r="C69">
         <v>265.01886677730067</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-9.4408621073144712</v>
+        <v>-9.3295423826991382</v>
       </c>
       <c r="B70">
-        <v>2.1709703286518502</v>
+        <v>2.52001766038444</v>
       </c>
       <c r="C70">
         <v>265.01886677730067</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-10.959954246661237</v>
+        <v>-10.847071767395367</v>
       </c>
       <c r="B71">
-        <v>2.6432621285279576</v>
+        <v>2.9974876141005424</v>
       </c>
       <c r="C71">
         <v>265.01886677730067</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-12.47822652009334</v>
+        <v>-12.364472141592522</v>
       </c>
       <c r="B72">
-        <v>3.118054946610445</v>
+        <v>3.4753439509495392</v>
       </c>
       <c r="C72">
         <v>265.01886677730067</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-13.996617814562713</v>
+        <v>-13.882379961155268</v>
       </c>
       <c r="B73">
-        <v>3.5924846885168886</v>
+        <v>3.9516805019552317</v>
       </c>
       <c r="C73">
         <v>265.01886677730067</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-15.514741741929788</v>
+        <v>-15.400533419913096</v>
       </c>
       <c r="B74">
-        <v>4.0677300393890024</v>
+        <v>4.4272813698774751</v>
       </c>
       <c r="C74">
         <v>265.01886677730067</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-17.031873340630231</v>
+        <v>-16.9184412317329</v>
       </c>
       <c r="B75">
-        <v>4.5460025097175123</v>
+        <v>4.9036179440730638</v>
       </c>
       <c r="C75">
         <v>265.01886677730067</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-18.54725863049233</v>
+        <v>-18.435592452666462</v>
       </c>
       <c r="B76">
-        <v>5.029602131865083</v>
+        <v>5.3822204885505167</v>
       </c>
       <c r="C76">
         <v>265.01886677730067</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-20.060199471776691</v>
+        <v>-19.951513993092448</v>
       </c>
       <c r="B77">
-        <v>5.520658595781641</v>
+        <v>5.8645058945809847</v>
       </c>
       <c r="C77">
         <v>265.01886677730067</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-21.570250105080884</v>
+        <v>-21.465903838512357</v>
       </c>
       <c r="B78">
-        <v>6.020531699894244</v>
+        <v>6.3513786878344627</v>
       </c>
       <c r="C78">
         <v>265.01886677730067</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-23.076651094627156</v>
+        <v>-22.978247369414248</v>
       </c>
       <c r="B79">
-        <v>6.531538119006381</v>
+        <v>6.8443801405384166</v>
       </c>
       <c r="C79">
         <v>265.01886677730067</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-24.578070561510124</v>
+        <v>-24.487641973963353</v>
       </c>
       <c r="B80">
-        <v>7.0577407777151846</v>
+        <v>7.34621355196702</v>
       </c>
       <c r="C80">
         <v>265.01886677730067</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-26.071238729322356</v>
+        <v>-25.991871539177087</v>
       </c>
       <c r="B81">
-        <v>7.6091141976826586</v>
+        <v>7.86351612361319</v>
       </c>
       <c r="C81">
         <v>265.01886677730067</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-27.497292372826667</v>
+        <v>-27.45103866038054</v>
       </c>
       <c r="B82">
-        <v>8.365221884807454</v>
+        <v>8.5157795582710012</v>
       </c>
       <c r="C82">
         <v>265.01886677730067</v>
